--- a/evaluation_forms/038_nursing_evaluation_and_self_assessment--evaluation_forms.xlsx
+++ b/evaluation_forms/038_nursing_evaluation_and_self_assessment--evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'satisfactory'}</t>
+          <t>satisfactory</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Satisfactory'}</t>
+          <t>Satisfactory</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'needs_improvement'}</t>
+          <t>needs_improvement</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Needs Improvement'}</t>
+          <t>Needs Improvement</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'time_management'}</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Time Management'}</t>
+          <t>Time Management</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'communication'}</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Communication'}</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'problem_solving'}</t>
+          <t>problem_solving</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Problem Solving'}</t>
+          <t>Problem Solving</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'leadership'}</t>
+          <t>leadership</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Leadership'}</t>
+          <t>Leadership</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'teamwork'}</t>
+          <t>teamwork</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Teamwork'}</t>
+          <t>Teamwork</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'adaptability'}</t>
+          <t>adaptability</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Adaptability'}</t>
+          <t>Adaptability</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'emotional_intelligence'}</t>
+          <t>emotional_intelligence</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Emotional Intelligence'}</t>
+          <t>Emotional Intelligence</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'conflict_resolution'}</t>
+          <t>conflict_resolution</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Conflict Resolution'}</t>
+          <t>Conflict Resolution</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'delegation'}</t>
+          <t>delegation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Delegation'}</t>
+          <t>Delegation</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'empathy'}</t>
+          <t>empathy</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Empathy'}</t>
+          <t>Empathy</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'flexibility'}</t>
+          <t>flexibility</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Flexibility'}</t>
+          <t>Flexibility</t>
         </is>
       </c>
     </row>
